--- a/ZlaataQA/reports/Automation_Report.xlsx
+++ b/ZlaataQA/reports/Automation_Report.xlsx
@@ -22,13 +22,14 @@
     <sheet name="2026-07-10" r:id="rId10" sheetId="49"/>
     <sheet name="2026-07-14" r:id="rId11" sheetId="50"/>
     <sheet name="2026-07-20" r:id="rId12" sheetId="51"/>
+    <sheet name="2026-07-27" r:id="rId13" sheetId="52"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1324" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="120">
   <si>
     <t>TestCase Name</t>
   </si>
@@ -319,6 +320,75 @@
   </si>
   <si>
     <t>TOTAL TIME EXECUTED : 205 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_02 |Verify that stock changes are reflected and saved successfully after adjusting stock on Raw Material Sectio.|"TD_UI_Zlaata_Raw_02"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 23 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_02 |Verify that stock changes are reflected and saved successfully after adjusting stock on Raw Material Section.|"TD_UI_Zlaata_Raw_02"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 60 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 123 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 70 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 45 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 31 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 42 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_03 |Verify that stock changes are reflected and saved successfully after adding stock on Raw Material Section.| "TD_UI_Zlaata_Raw_03"</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_04</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Raw_04 |Verify that the low stock alert is saved and reflected successfully on Raw Material Section.| "TD_UI_Zlaata_Raw_04"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 48 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 37 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 52 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 57 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 83 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Atbs_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_Atbs_01 |Verify admin can add a new Attributes successfully.|"TD_UI_Zlaata_Atbs_01"</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: Attributes</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 26 sec</t>
   </si>
 </sst>
 </file>
@@ -326,7 +396,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="84" x14ac:knownFonts="1">
+  <fonts count="108" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -353,6 +423,126 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -800,7 +990,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="243">
+  <cellXfs count="313">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1062,6 +1252,78 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="86" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="96" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="97" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="98" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="99" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="100" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="101" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="102" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="103" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="104" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="105" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="106" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2396,6 +2658,505 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>147996</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -7444,11 +8205,11 @@
 
 <file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="116.98828125"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="142.15625"/>
     <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
     <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
     <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
@@ -7465,38 +8226,38 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="242">
+      <c r="A1" t="s" s="248">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="242">
+      <c r="A2" t="s" s="248">
         <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="242">
-        <v>35</v>
+      <c r="A3" t="s" s="248">
+        <v>29</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="242">
+      <c r="A4" t="s" s="248">
         <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="242">
+      <c r="A5" t="s" s="248">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="242">
+      <c r="A6" t="s" s="248">
         <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="242">
-        <v>96</v>
+      <c r="A7" t="s" s="248">
+        <v>36</v>
       </c>
       <c r="B7" t="s" s="233">
         <v>0</v>
@@ -7752,6 +8513,1171 @@
         <v>0.0</v>
       </c>
       <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>98</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>23.661</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s" s="244">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>0.029</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s" s="246">
+        <v>17</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O28"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="142.15625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="312">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="312">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="312">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="312">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="312">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="312">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="312">
+        <v>119</v>
+      </c>
+      <c r="B7" t="s" s="249">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s" s="249">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s" s="249">
+        <v>2</v>
+      </c>
+      <c r="E7" t="s" s="249">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s" s="249">
+        <v>4</v>
+      </c>
+      <c r="G7" t="s" s="249">
+        <v>5</v>
+      </c>
+      <c r="H7" t="s" s="249">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>60.845</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E8" t="s" s="251">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>33.792</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E9" t="s" s="254">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>123.259</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E10" t="s" s="257">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>70.949</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E11" t="s" s="260">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>51.574</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E12" t="s" s="263">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>45.116</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E13" t="s" s="266">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>31.839</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E14" t="s" s="269">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>31.625</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E15" t="s" s="272">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>97</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>42.872</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E16" t="s" s="274">
+        <v>17</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>0.048</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E17" t="s" s="278">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>0.032</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E18" t="s" s="280">
+        <v>17</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>0.048</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E19" t="s" s="283">
+        <v>17</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C20" t="n" s="0">
+        <v>33.892</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E20" t="s" s="286">
+        <v>17</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O20" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C21" t="n" s="0">
+        <v>48.873</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E21" t="s" s="290">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O21" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B22" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C22" t="n" s="0">
+        <v>37.765</v>
+      </c>
+      <c r="D22" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E22" t="s" s="293">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H22" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N22" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O22" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B23" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C23" t="n" s="0">
+        <v>52.591</v>
+      </c>
+      <c r="D23" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E23" t="s" s="295">
+        <v>17</v>
+      </c>
+      <c r="F23" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H23" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N23" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O23" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="B24" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="C24" t="n" s="0">
+        <v>42.466</v>
+      </c>
+      <c r="D24" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E24" t="s" s="298">
+        <v>17</v>
+      </c>
+      <c r="F24" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H24" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N24" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O24" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B25" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C25" t="n" s="0">
+        <v>57.218</v>
+      </c>
+      <c r="D25" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E25" t="s" s="302">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H25" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N25" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O25" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="B26" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="C26" t="n" s="0">
+        <v>83.551</v>
+      </c>
+      <c r="D26" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E26" t="s" s="304">
+        <v>17</v>
+      </c>
+      <c r="F26" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H26" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N26" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O26" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B27" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C27" t="n" s="0">
+        <v>0.047</v>
+      </c>
+      <c r="D27" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E27" t="s" s="307">
+        <v>17</v>
+      </c>
+      <c r="F27" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H27" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N27" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O27" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C28" t="n" s="0">
+        <v>26.324</v>
+      </c>
+      <c r="D28" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E28" t="s" s="310">
+        <v>17</v>
+      </c>
+      <c r="F28" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H28" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N28" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O28" t="s" s="0">
         <v>10</v>
       </c>
     </row>

--- a/ZlaataQA/reports/Automation_Report.xlsx
+++ b/ZlaataQA/reports/Automation_Report.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1677" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1737" uniqueCount="122">
   <si>
     <t>TestCase Name</t>
   </si>
@@ -389,6 +389,12 @@
   </si>
   <si>
     <t>TOTAL TIME EXECUTED : 26 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 34 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 43 sec</t>
   </si>
 </sst>
 </file>
@@ -396,7 +402,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="0"/>
-  <fonts count="108" x14ac:knownFonts="1">
+  <fonts count="112" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color indexed="8"/>
@@ -423,6 +429,26 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -990,7 +1016,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="313">
+  <cellXfs count="325">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1324,6 +1350,18 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="107" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="108" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="109" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="110" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="111" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3157,6 +3195,82 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8618,7 +8732,7 @@
 
 <file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O28"/>
+  <dimension ref="A1:O32"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" width="29.60546875"/>
@@ -8639,38 +8753,38 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s" s="312">
+      <c r="A1" t="s" s="324">
         <v>15</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s" s="312">
+      <c r="A2" t="s" s="324">
         <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="s" s="312">
+      <c r="A3" t="s" s="324">
         <v>118</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="s" s="312">
+      <c r="A4" t="s" s="324">
         <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="s" s="312">
+      <c r="A5" t="s" s="324">
         <v>18</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="s" s="312">
+      <c r="A6" t="s" s="324">
         <v>16</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s" s="312">
-        <v>119</v>
+      <c r="A7" t="s" s="324">
+        <v>121</v>
       </c>
       <c r="B7" t="s" s="249">
         <v>0</v>
@@ -9678,6 +9792,194 @@
         <v>0.0</v>
       </c>
       <c r="O28" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C29" t="n" s="0">
+        <v>34.596</v>
+      </c>
+      <c r="D29" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E29" t="s" s="314">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H29" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N29" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O29" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B30" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C30" t="n" s="0">
+        <v>31.97</v>
+      </c>
+      <c r="D30" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E30" t="s" s="317">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H30" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N30" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O30" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B31" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C31" t="n" s="0">
+        <v>42.467</v>
+      </c>
+      <c r="D31" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E31" t="s" s="319">
+        <v>17</v>
+      </c>
+      <c r="F31" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H31" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N31" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O31" t="s" s="0">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="B32" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="C32" t="n" s="0">
+        <v>43.761</v>
+      </c>
+      <c r="D32" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="E32" t="s" s="322">
+        <v>17</v>
+      </c>
+      <c r="F32" t="s" s="0">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="H32" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="I32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N32" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O32" t="s" s="0">
         <v>10</v>
       </c>
     </row>

--- a/ZlaataQA/reports/Automation_Report.xlsx
+++ b/ZlaataQA/reports/Automation_Report.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="2026-09-09" r:id="rId3" sheetId="1"/>
     <sheet name="2026-09-10" r:id="rId4" sheetId="2"/>
+    <sheet name="2026-10-09" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="667" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="862" uniqueCount="79">
   <si>
     <t>TestCase ID</t>
   </si>
@@ -220,6 +221,36 @@
   </si>
   <si>
     <t>TOTAL TIME EXECUTED : 75 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_01</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_01 |Verify that product is successfully archived and displayed in the Product Archive section.| "TD_UI_Zlaata_PA_01"</t>
+  </si>
+  <si>
+    <t>FEATURE FILES: ProductArchieve</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 41 sec</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 42 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_02</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_02 |Verify that an archived product is successfully restored and displayed in the Product Listing section.| "TD_UI_Zlaata_PA_02"</t>
+  </si>
+  <si>
+    <t>TOTAL TIME EXECUTED : 64 sec</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_03</t>
+  </si>
+  <si>
+    <t>TC_UI_Zlaata_PA_03 |Verify that archived products are successfully restored using the Bulk Restore option.| "TD_UI_Zlaata_PA_03"</t>
   </si>
 </sst>
 </file>
@@ -227,13 +258,83 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="48">
+  <fonts count="62">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="11.0"/>
+      <b val="true"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -521,7 +622,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="138">
+  <cellXfs count="178">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -664,6 +765,48 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
     <xf numFmtId="0" fontId="47" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="48" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="51" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="55" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="57" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="0" xfId="0" applyFont="true"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="true"/>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
@@ -1585,6 +1728,315 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="1" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="twoCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>71145</xdr:colOff>
+      <xdr:row>62</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Picture 1" descr="Picture"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="true"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="18288000" cy="8686800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:O9"/>
@@ -3724,4 +4176,652 @@
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:O19"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" bestFit="true" customWidth="true" width="30.7421875"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" width="131.98046875"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" width="11.90234375"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" width="12.171875"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" width="6.765625"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="15.03515625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" width="11.19921875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" width="2.15234375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" width="1.0390625"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="177">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="177">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="177">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="177">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="177">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="177">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="177">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s" s="138">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s" s="138">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s" s="138">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s" s="138">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s" s="138">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s" s="138">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s" s="138">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>0.079</v>
+      </c>
+      <c r="D8" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E8" t="s" s="139">
+        <v>18</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>32.318</v>
+      </c>
+      <c r="D9" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E9" t="s" s="143">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N9" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>35.867</v>
+      </c>
+      <c r="D10" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E10" t="s" s="146">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>36.424</v>
+      </c>
+      <c r="D11" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s" s="149">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N11" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C12" t="n" s="0">
+        <v>15.623</v>
+      </c>
+      <c r="D12" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s" s="152">
+        <v>26</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N12" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>41.614</v>
+      </c>
+      <c r="D13" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E13" t="s" s="155">
+        <v>26</v>
+      </c>
+      <c r="F13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N13" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O13" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>36.824</v>
+      </c>
+      <c r="D14" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E14" t="s" s="158">
+        <v>26</v>
+      </c>
+      <c r="F14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>48.706</v>
+      </c>
+      <c r="D15" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E15" t="s" s="161">
+        <v>26</v>
+      </c>
+      <c r="F15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N15" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O15" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>70</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>42.904</v>
+      </c>
+      <c r="D16" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E16" t="s" s="163">
+        <v>18</v>
+      </c>
+      <c r="F16" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N16" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B17" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C17" t="n" s="0">
+        <v>0.051</v>
+      </c>
+      <c r="D17" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s" s="166">
+        <v>18</v>
+      </c>
+      <c r="F17" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G17" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H17" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N17" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O17" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="0">
+        <v>74</v>
+      </c>
+      <c r="B18" t="s" s="0">
+        <v>75</v>
+      </c>
+      <c r="C18" t="n" s="0">
+        <v>64.544</v>
+      </c>
+      <c r="D18" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s" s="173">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G18" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H18" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N18" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O18" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>77</v>
+      </c>
+      <c r="B19" t="s" s="0">
+        <v>78</v>
+      </c>
+      <c r="C19" t="n" s="0">
+        <v>0.034</v>
+      </c>
+      <c r="D19" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E19" t="s" s="175">
+        <v>18</v>
+      </c>
+      <c r="F19" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="G19" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="H19" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="I19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="J19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="K19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="M19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="N19" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="O19" t="s" s="0">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>